--- a/LLM_Extraction_and_CrossCritique/interactive-table/gt-vs-runs_pipeline4.xlsx
+++ b/LLM_Extraction_and_CrossCritique/interactive-table/gt-vs-runs_pipeline4.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="505" uniqueCount="357">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="505" uniqueCount="398">
   <si>
     <t>Query</t>
   </si>
@@ -2070,8 +2070,8 @@
   <si>
     <t>{
   "selected_filter": {
-    "ICI Class": "PD-1",
-    "Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)"
+    "Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)",
+    "ICI Class": "PD-1"
   },
   "selected_column": {
     "Column 1": "NCT",
@@ -2079,7 +2079,9 @@
     "Column 3": "Authors",
     "Column 4": "Year",
     "Column 5": "Treatment regimen",
-    "Column 6": "ICI Name"
+    "Column 6": "Name of ICI",
+    "Column 7": "Monotherapy/combination",
+    "Column 8": "Lines of treatment"
   }
 }</t>
   </si>
@@ -2087,15 +2089,18 @@
     <t>{
   "selected_filter": {
     "Cancer Type": "Melanoma",
-    "Type of Therapy": "Combination"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "ICI Name",
-    "Column 6": "Clinical Setting"
+    "Type of combination (Treatment Arm)": "ICI + ICI"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Study name",
+    "Column 6": "Name of ICI",
+    "Column 7": "Class of ICI",
+    "Column 8": "Treatment regimen",
+    "Column 9": "Clinical setting in relation to surgery"
   }
 }</t>
   </si>
@@ -2110,24 +2115,31 @@
     "Column 2": "PMID",
     "Column 3": "Authors",
     "Column 4": "Year",
-    "Column 5": "Total sample size",
-    "Column 6": "Primary endpoint"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer Type": "Bladder",
+    "Column 5": "Study name",
+    "Column 6": "Trial phase",
+    "Column 7": "Total sample size",
+    "Column 8": "Primary endpoint"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
     "Trial Phase": "Phase 3",
-    "Type of Therapy": "Monotherapy"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Follow-up duration for primary endpoint(s) in months"
+    "Type of Therapy": "Monotherapy",
+    "Cancer Type": "Urothelial and Bladder"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Study name",
+    "Column 6": "Name of ICI",
+    "Column 7": "Class of ICI",
+    "Column 8": "Primary endpoint",
+    "Column 9": "Clinical setting in relation to surgery",
+    "Column 10": "Follow-up duration for primary endpoint(s) in months"
   }
 }</t>
   </si>
@@ -2144,15 +2156,17 @@
     "Column 4": "Year",
     "Column 5": "Treatment regimen",
     "Column 6": "Control regimen",
-    "Column 7": "Primary Endpoint"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "ICI Class": "CTLA-4",
-    "Cancer Type": "Renal Cell Carcinoma (RCC)"
+    "Column 7": "Trial phase",
+    "Column 8": "Primary endpoint"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer Type": "Renal Cell Carcinoma (RCC)",
+    "Type of Therapy": "Combination",
+    "Type of combination (Treatment Arm)": "ICI + ICI"
   },
   "selected_column": {
     "Column 1": "NCT",
@@ -2160,7 +2174,10 @@
     "Column 3": "Authors",
     "Column 4": "Year",
     "Column 5": "Treatment regimen",
-    "Column 6": "Control regimen"
+    "Column 6": "Name of ICI",
+    "Column 7": "Class of ICI",
+    "Column 8": "Control regimen",
+    "Column 9": "Type of control"
   }
 }</t>
   </si>
@@ -2174,17 +2191,20 @@
     "Column 2": "PMID",
     "Column 3": "Authors",
     "Column 4": "Year",
-    "Column 5": "Cancer Type",
-    "Column 6": "Type of Therapy",
-    "Column 7": "ICI Name",
-    "Column 8": "Type of Combination (Treatment Arm)",
-    "Column 9": "Control Arm"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {},
+    "Column 5": "ICI Name",
+    "Column 6": "Cancer Type",
+    "Column 7": "Type of combination (Treatment Arm)",
+    "Column 8": "Control Arm",
+    "Column 9": "Primary Endpoint",
+    "Column 10": "Trial Phase"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Total sample size": "&gt;= 500"
+  },
   "selected_column": {
     "Column 1": "NCT",
     "Column 2": "PMID",
@@ -2198,26 +2218,33 @@
   <si>
     <t>{
   "selected_filter": {
-    "Primary Endpoint": "Overall Survival"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Cancer Type",
-    "Column 6": "Treatment regimen"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {},
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year"
+    "Primary Endpoint": "OS"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Treatment regimen",
+    "Column 6": "Control regimen",
+    "Column 7": "Cancer type",
+    "Column 8": "Lines of treatment",
+    "Column 9": "Monotherapy/combination",
+    "Column 10": "Type of combination"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Year": "&gt;2020"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Study name"
   }
 }</t>
   </si>
@@ -2232,8 +2259,11 @@
     "Column 2": "PMID",
     "Column 3": "Authors",
     "Column 4": "Year",
-    "Column 5": "Cancer Type",
-    "Column 6": "Primary Endpoint"
+    "Column 5": "Cancer type",
+    "Column 6": "Name of ICI",
+    "Column 7": "Trial phase",
+    "Column 8": "Primary endpoint",
+    "Column 9": "Secondary endpoint"
   }
 }</t>
   </si>
@@ -2241,6 +2271,43 @@
     <t>{
   "selected_filter": {
     "ICI Class": "PD-L1",
+    "Type of Therapy": "Combination"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Cancer type",
+    "Column 6": "ICI Name",
+    "Column 7": "Type of combination (Treatment Arm)"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "ICI Class": "CTLA-4",
+    "Type of Therapy": "Monotherapy"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Class of ICI",
+    "Column 6": "Name of ICI",
+    "Column 7": "Monotherapy/combination",
+    "Column 8": "Cancer type",
+    "Column 9": "Treatment regimen",
+    "Column 10": "Trial phase"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "ICI Class": "CTLA-4",
     "Type of Therapy": "Combination"
   },
   "selected_column": {
@@ -2251,72 +2318,46 @@
     "Column 5": "Cancer Type",
     "Column 6": "ICI Name",
     "Column 7": "Type of combination (Treatment Arm)",
-    "Column 8": "Primary Endpoint"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "ICI Class": "CTLA-4",
-    "Type of Therapy": "Monotherapy"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Cancer Type",
-    "Column 6": "ICI Name"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "ICI Class": "CTLA-4",
-    "Type of Therapy": "Combination"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Cancer Type",
-    "Column 6": "Type of combination (Treatment Arm)",
-    "Column 7": "Primary Endpoint"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer Type": "Head and Neck (HNSCC)",
-    "ICI Class": "PD-L1"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Name of ICI"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
+    "Column 8": "Trial Phase"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer Type": "Head and Neck (HNSCC)"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "ICI Class",
+    "Column 6": "ICI Name",
+    "Column 7": "Type of combination (Treatment Arm)",
+    "Column 8": "Control Arm",
+    "Column 9": "Trial Phase"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Trial Phase": "Phase 3",
     "ICI Name": "Pembrolizumab",
-    "Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)",
-    "Trial Phase": "Phase 3"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Primary Endpoint",
-    "Column 6": "Type of Therapy"
+    "Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Study name",
+    "Column 6": "Treatment regimen",
+    "Column 7": "Control regimen",
+    "Column 8": "Monotherapy/combination",
+    "Column 9": "Lines of treatment",
+    "Column 10": "Primary endpoint"
   }
 }</t>
   </si>
@@ -2331,8 +2372,12 @@
     "Column 2": "PMID",
     "Column 3": "Authors",
     "Column 4": "Year",
-    "Column 5": "Type of Therapy",
-    "Column 6": "Type of combination (Treatment Arm)"
+    "Column 5": "Type of combination (Treatment Arm)",
+    "Column 6": "Treatment regimen",
+    "Column 7": "Control Arm",
+    "Column 8": "Trial Phase",
+    "Column 9": "Primary Endpoint",
+    "Column 10": "Clinical Setting"
   }
 }</t>
   </si>
@@ -2341,17 +2386,19 @@
   "selected_filter": {
     "ICI Name": "Atezolizumab",
     "Type of combination (Treatment Arm)": "ICI + Chemo",
-    "Cancer Type": "Breast"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Cancer Type",
+    "Cancer Type": "Triple-negative breast cancer"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Is PD-L1 positivity inclusion criteria",
     "Column 6": "Treatment regimen",
-    "Column 7": "Name of ICI",
-    "Column 8": "Is PD-L1 positivity inclusion criteria"
+    "Column 7": "Trial Phase",
+    "Column 8": "Clinical Setting",
+    "Column 9": "Primary Endpoint",
+    "Column 10": "Control Arm"
   }
 }</t>
   </si>
@@ -2366,7 +2413,8 @@
     "Column 2": "PMID",
     "Column 3": "Authors",
     "Column 4": "Year",
-    "Column 5": "Clinical Setting"
+    "Column 5": "Clinical Setting",
+    "Column 6": "Trial Phase"
   }
 }</t>
   </si>
@@ -2374,16 +2422,19 @@
     <t>{
   "selected_filter": {
     "ICI Name": "Tremelimumab",
-    "Cancer Type": "Hepatocellular carcinoma (HCC)"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Type of combination (Treatment Arm)",
-    "Column 6": "Control Arm",
-    "Column 7": "Primary Endpoint"
+    "Cancer Type": "Hepatocellular carcinoma (HCC)",
+    "Type of Therapy": "Combination",
+    "Type of combination (Treatment Arm)": "ICI + ICI"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Trial phase",
+    "Column 6": "Treatment regimen",
+    "Column 7": "Primary endpoint",
+    "Column 8": "Total sample size"
   }
 }</t>
   </si>
@@ -2391,36 +2442,36 @@
     <t>{
   "selected_filter": {
     "ICI Name": "Durvalumab",
+    "Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)",
+    "Type of Therapy": "Monotherapy",
     "Clinical Setting": "Maintenance",
-    "Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Type of Therapy",
-    "Column 6": "Trial Phase",
-    "Column 7": "Primary Endpoint"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
+    "Trial Phase": "Phase 3"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Study name",
+    "Column 6": "Treatment regimen"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Trial Phase": "Phase 3",
     "ICI Class": "PD-1",
     "Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)",
-    "Type of Therapy": "Combination",
-    "Trial Phase": "Phase 3"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Type of combination (Treatment Arm)",
-    "Column 6": "Total sample size",
-    "Column 7": "Primary Endpoint"
+    "Type of Therapy": "Combination"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Total sample size",
+    "Column 6": "Primary endpoint"
   }
 }</t>
   </si>
@@ -2435,15 +2486,71 @@
     "Column 2": "PMID",
     "Column 3": "Authors",
     "Column 4": "Year",
+    "Column 5": "Cancer type",
+    "Column 6": "Name of ICI"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Type of combination (Treatment Arm)": "PD-1 + CTLA-4 combination"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Cancer type",
+    "Column 6": "Class of ICI",
+    "Column 7": "Name of ICI",
+    "Column 8": "Type of combination",
+    "Column 9": "Treatment regimen",
+    "Column 10": "Trial phase"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)",
+    "Type of Therapy": "Combination",
+    "Type of combination (Treatment Arm)": "ICI + Chemo"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Primary endpoint",
+    "Column 6": "Name of ICI",
+    "Column 7": "Treatment regimen",
+    "Column 8": "Lines of treatment"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Type of combination (Treatment Arm)": "ICI + TKI (Tyrosine Kinase Inhibitor)"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
     "Column 5": "Cancer Type",
-    "Column 6": "ICI Name"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Type of combination (Treatment Arm)": "ICI + ICI"
+    "Column 6": "Name of ICI",
+    "Column 7": "Treatment regimen",
+    "Column 8": "Trial Phase",
+    "Column 9": "Primary Endpoint"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Type of combination (Treatment Arm)": "ICI + Radiation"
   },
   "selected_column": {
     "Column 1": "NCT",
@@ -2451,55 +2558,11 @@
     "Column 3": "Authors",
     "Column 4": "Year",
     "Column 5": "Cancer Type",
-    "Column 6": "ICI Name"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)",
-    "Type of combination (Treatment Arm)": "ICI + Chemo"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Primary Endpoint"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Type of combination (Treatment Arm)": "ICI + TKI (Tyrosine Kinase Inhibitor)"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Cancer Type",
-    "Column 6": "Type of Therapy",
-    "Column 7": "ICI Name"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Type of combination (Treatment Arm)": "ICI + RadiatICln (Radiation/Clinical Radiation)"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Cancer Type",
-    "Column 6": "Type of Therapy",
+    "Column 6": "Treatment Regimen",
     "Column 7": "ICI Name",
-    "Column 8": "Primary Endpoint"
+    "Column 8": "ICI Class",
+    "Column 9": "Trial Phase",
+    "Column 10": "Primary Endpoint"
   }
 }</t>
   </si>
@@ -2513,9 +2576,12 @@
     "Column 2": "PMID",
     "Column 3": "Authors",
     "Column 4": "Year",
-    "Column 5": "Cancer Type",
-    "Column 6": "Type of Therapy",
-    "Column 7": "Primary Endpoint"
+    "Column 5": "Study name",
+    "Column 6": "Cancer type",
+    "Column 7": "Treatment regimen",
+    "Column 8": "Name of ICI",
+    "Column 9": "Class of ICI",
+    "Column 10": "Trial phase"
   }
 }</t>
   </si>
@@ -2530,8 +2596,10 @@
     "Column 2": "PMID",
     "Column 3": "Authors",
     "Column 4": "Year",
-    "Column 5": "Primary Endpoint",
-    "Column 6": "Trial Phase"
+    "Column 5": "Treatment regimen",
+    "Column 6": "Name of ICI",
+    "Column 7": "Trial phase",
+    "Column 8": "Clinical Setting"
   }
 }</t>
   </si>
@@ -2545,10 +2613,12 @@
     "Column 2": "PMID",
     "Column 3": "Authors",
     "Column 4": "Year",
-    "Column 5": "Cancer Type",
-    "Column 6": "Treatment regimen",
-    "Column 7": "Primary Endpoint",
-    "Column 8": "Total sample size"
+    "Column 5": "Study name",
+    "Column 6": "Cancer type",
+    "Column 7": "Treatment regimen",
+    "Column 8": "Name of ICI",
+    "Column 9": "Control regimen",
+    "Column 10": "Primary endpoint"
   }
 }</t>
   </si>
@@ -2562,7 +2632,12 @@
     "Column 2": "PMID",
     "Column 3": "Authors",
     "Column 4": "Year",
-    "Column 5": "Cancer Type"
+    "Column 5": "Cancer type",
+    "Column 6": "Type of combination",
+    "Column 7": "Treatment regimen",
+    "Column 8": "Name of ICI",
+    "Column 9": "Lines of treatment",
+    "Column 10": "Clinical setting in relation to surgery"
   }
 }</t>
   </si>
@@ -2576,8 +2651,11 @@
     "Column 2": "PMID",
     "Column 3": "Authors",
     "Column 4": "Year",
-    "Column 5": "Cancer Type",
-    "Column 6": "Type of combination (Treatment Arm)"
+    "Column 5": "Study name",
+    "Column 6": "Cancer type",
+    "Column 7": "Treatment regimen",
+    "Column 8": "Name of ICI",
+    "Column 9": "Class of ICI"
   }
 }</t>
   </si>
@@ -2592,9 +2670,10 @@
     "Column 2": "PMID",
     "Column 3": "Authors",
     "Column 4": "Year",
-    "Column 5": "Cancer Type",
-    "Column 6": "ICI Name",
-    "Column 7": "Primary Endpoint"
+    "Column 5": "Study name",
+    "Column 6": "Cancer type",
+    "Column 7": "Name of ICI",
+    "Column 8": "Class of ICI"
   }
 }</t>
   </si>
@@ -2609,10 +2688,11 @@
     "Column 2": "PMID",
     "Column 3": "Authors",
     "Column 4": "Year",
-    "Column 5": "Control Arm",
-    "Column 6": "Treatment Arm",
-    "Column 7": "Trial Phase",
-    "Column 8": "Total Sample Size"
+    "Column 5": "Control regimen",
+    "Column 6": "Type of control",
+    "Column 7": "Treatment regimen",
+    "Column 8": "Trial phase",
+    "Column 9": "Lines of treatment"
   }
 }</t>
   </si>
@@ -2620,33 +2700,35 @@
     <t>{
   "selected_filter": {
     "Cancer Type": "Hepatocellular carcinoma (HCC)",
-    "Control Arm": "TKI (Tyrosine Kinase Inhibitor)"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Primary Endpoint",
-    "Column 6": "Trial Phase"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Control Arm": "Interferon"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Cancer Type",
+    "Control Arm": "TKI"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Trial phase",
     "Column 6": "Treatment regimen",
     "Column 7": "Control regimen",
-    "Column 8": "Trial Phase",
-    "Column 9": "Primary Endpoint"
+    "Column 8": "Primary endpoint"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Control Arm": "Interferon"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Control regimen",
+    "Column 6": "Cancer type",
+    "Column 7": "Treatment regimen",
+    "Column 8": "Study name",
+    "Column 9": "Trial phase"
   }
 }</t>
   </si>
@@ -2660,26 +2742,29 @@
     "Column 2": "PMID",
     "Column 3": "Authors",
     "Column 4": "Year",
-    "Column 5": "Cancer Type",
-    "Column 6": "Primary Endpoint"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Control Arm": "Chemo / Anti-EGFR",
-    "Type of Therapy": "ICI"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Cancer Type",
+    "Column 5": "Control regimen",
+    "Column 6": "Treatment regimen",
+    "Column 7": "Cancer type",
+    "Column 8": "Primary endpoint",
+    "Column 9": "Trial phase"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Control Arm": "Chemo / Anti-EGFR"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Cancer type",
     "Column 6": "Treatment regimen",
     "Column 7": "Control regimen",
-    "Column 8": "Primary Endpoint"
+    "Column 8": "Lines of treatment",
+    "Column 9": "Trial phase"
   }
 }</t>
   </si>
@@ -2693,25 +2778,28 @@
     "Column 2": "PMID",
     "Column 3": "Authors",
     "Column 4": "Year",
-    "Column 5": "Cancer Type",
-    "Column 6": "Trial Phase",
-    "Column 7": "Primary Endpoint"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Control Arm": "mTOR inhibitor"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Cancer Type",
-    "Column 6": "Control Arm",
-    "Column 7": "Primary Endpoint"
+    "Column 5": "Control regimen",
+    "Column 6": "Treatment regimen",
+    "Column 7": "Cancer type",
+    "Column 8": "Trial phase",
+    "Column 9": "Primary endpoint"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Control Arm": "mTOR inhibitor",
+    "Cancer Type": "Renal Cell Carcinoma (RCC)"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Cancer type",
+    "Column 6": "Control regimen",
+    "Column 7": "Type of control"
   }
 }</t>
   </si>
@@ -2725,8 +2813,11 @@
     "Column 2": "PMID",
     "Column 3": "Authors",
     "Column 4": "Year",
-    "Column 5": "Cancer Type",
-    "Column 6": "Primary Endpoint"
+    "Column 5": "Control regimen",
+    "Column 6": "Treatment regimen",
+    "Column 7": "Cancer type",
+    "Column 8": "Primary endpoint",
+    "Column 9": "Trial phase"
   }
 }</t>
   </si>
@@ -2740,8 +2831,11 @@
     "Column 2": "PMID",
     "Column 3": "Authors",
     "Column 4": "Year",
-    "Column 5": "Cancer Type",
-    "Column 6": "Primary Endpoint"
+    "Column 5": "Cancer type",
+    "Column 6": "Trial phase",
+    "Column 7": "Treatment regimen",
+    "Column 8": "Control regimen",
+    "Column 9": "Primary endpoint"
   }
 }</t>
   </si>
@@ -2755,203 +2849,15 @@
     "Column 2": "PMID",
     "Column 3": "Authors",
     "Column 4": "Year",
-    "Column 5": "Cancer Type",
-    "Column 6": "Control Arm"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Clinical Setting": "Adjuvant",
-    "Cancer Type": "Melanoma"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Type of Therapy",
-    "Column 6": "ICI Name",
-    "Column 7": "Type of combination (Treatment Arm)"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)",
-    "Clinical Setting": "Neoadjuvant"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Primary Endpoint"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Primary Endpoint": "Path CR (Pathologic Complete Response; pCR)"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Cancer Type",
-    "Column 6": "Clinical Setting"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Primary Endpoint": "ORR (Objective Response Rate)"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Cancer Type",
-    "Column 6": "Trial Phase"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Primary Endpoint": "OS"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Cancer Type",
-    "Column 6": "Total sample size",
-    "Column 7": "Follow-up duration for primary endpoint(s) in months"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Primary Endpoint": "PFS (Progression-Free Survival)"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Cancer Type",
-    "Column 6": "Trial Phase",
-    "Column 7": "Primary Endpoint"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Primary Endpoint": "RFS (Recurrence-/Relapse-Free Survival)"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Cancer Type",
-    "Column 6": "Primary Endpoint"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Primary Endpoint": "EFS (Event-Free Survival)"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Cancer Type",
-    "Column 6": "Primary Endpoint"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Primary Endpoint": "Safety"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Cancer Type",
-    "Column 6": "Treatment regimen"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Is PD-L1 positivity inclusion criteria",
-    "Column 6": "Primary Endpoint"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer Type": "Colorectal",
-    "Included in MA": "Yes",
-    "Type of combination (Treatment Arm)": "ICI Combination"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "ICI Name",
-    "Column 6": "Primary Endpoint",
-    "Column 7": "Trial Phase"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer Type": "Pancreatic Cancer"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "ICI Name",
-    "Column 6": "Type of Therapy",
-    "Column 7": "Is any other biomarker used for inclusion"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer Type": "Prostate"
+    "Column 5": "Control regimen"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer Type": "Melanoma",
+    "Clinical Setting": "Adjuvant"
   },
   "selected_column": {
     "Column 1": "NCT",
@@ -2961,7 +2867,234 @@
     "Column 5": "ICI Name",
     "Column 6": "ICI Class",
     "Column 7": "Type of combination (Treatment Arm)",
-    "Column 8": "Primary Endpoint"
+    "Column 8": "Trial Phase"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)",
+    "Clinical Setting": "Neoadjuvant",
+    "Type of Therapy": "Immunotherapy"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Treatment regimen",
+    "Column 6": "Name of ICI",
+    "Column 7": "Primary endpoint",
+    "Column 8": "Trial phase"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Primary Endpoint": "Path CR"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Primary Endpoint",
+    "Column 6": "Cancer Type",
+    "Column 7": "Type of combination (Treatment Arm)",
+    "Column 8": "Control Arm",
+    "Column 9": "Clinical Setting",
+    "Column 10": "Trial Phase"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Primary Endpoint": "ORR"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Primary endpoint",
+    "Column 6": "Cancer type",
+    "Column 7": "Treatment regimen",
+    "Column 8": "Control regimen",
+    "Column 9": "Trial phase",
+    "Column 10": "Total sample size"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Primary Endpoint": "OS"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Study name",
+    "Column 6": "Cancer type",
+    "Column 7": "Trial phase",
+    "Column 8": "Treatment regimen",
+    "Column 9": "Control regimen"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Primary Endpoint": "PFS"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Primary endpoint",
+    "Column 6": "Cancer type",
+    "Column 7": "Treatment regimen",
+    "Column 8": "Control regimen",
+    "Column 9": "Trial phase",
+    "Column 10": "Lines of treatment"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Primary Endpoint": "RFS (Recurrence-/Relapse-Free Survival)"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Primary Endpoint",
+    "Column 6": "Cancer Type",
+    "Column 7": "Type of combination (Treatment Arm)",
+    "Column 8": "Control Arm",
+    "Column 9": "Clinical Setting",
+    "Column 10": "Trial Phase"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Primary Endpoint": "EFS"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Primary endpoint",
+    "Column 6": "Cancer type",
+    "Column 7": "Treatment regimen",
+    "Column 8": "Control regimen",
+    "Column 9": "Trial phase",
+    "Column 10": "Follow-up duration for primary endpoint(s) in months"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Primary Endpoint": "Safety"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Primary endpoint",
+    "Column 6": "Trial phase",
+    "Column 7": "Cancer type",
+    "Column 8": "Treatment regimen",
+    "Column 9": "Control regimen",
+    "Column 10": "Total sample size"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Study name",
+    "Column 6": "Treatment regimen",
+    "Column 7": "Name of ICI",
+    "Column 8": "Lines of treatment",
+    "Column 9": "Is PD-L1 positivity inclusion criteria"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer Type": "Colorectal",
+    "Type of Therapy": "Immunotherapy"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Treatment regimen",
+    "Column 6": "Name of ICI",
+    "Column 7": "Class of ICI",
+    "Column 8": "Is any other biomarker used for inclusion",
+    "Column 9": "Lines of treatment",
+    "Column 10": "Trial Phase"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer Type": "Pancreatic Cancer",
+    "Type of Therapy": "Immunotherapy"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Treatment regimen",
+    "Column 6": "Name of ICI",
+    "Column 7": "Class of ICI",
+    "Column 8": "Is PD-L1 positivity inclusion criteria",
+    "Column 9": "Is any other biomarker used for inclusion"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer Type": "Prostate"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "ICI Name",
+    "Column 6": "ICI Class",
+    "Column 7": "Type of combination (Treatment Arm)",
+    "Column 8": "Is PD-L1 positivity inclusion criteria",
+    "Column 9": "Is any other biomarker used for inclusion",
+    "Column 10": "Treatment regimen"
   }
 }</t>
   </si>
@@ -2975,22 +3108,30 @@
     "Column 2": "PMID",
     "Column 3": "Authors",
     "Column 4": "Year",
-    "Column 5": "Primary Endpoint"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer Type": "Mesothelioma"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Type of Therapy",
-    "Column 6": "Treatment regimen"
+    "Column 5": "Name of ICI",
+    "Column 6": "Class of ICI",
+    "Column 7": "Treatment regimen",
+    "Column 8": "Primary endpoint",
+    "Column 9": "Trial phase"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer Type": "Mesothelioma",
+    "Type of Therapy": "Immunotherapy"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Study name",
+    "Column 6": "Trial phase",
+    "Column 7": "Treatment regimen",
+    "Column 8": "Name of ICI",
+    "Column 9": "Type of combination (Treatment Arm)"
   }
 }</t>
   </si>
@@ -3007,8 +3148,168 @@
     "Column 4": "Year",
     "Column 5": "Original/Follow Up",
     "Column 6": "Study name",
-    "Column 7": "Follow-up duration for primary endpoint(s) in months",
-    "Column 8": "Primary Endpoint"
+    "Column 7": "Treatment regimen",
+    "Column 8": "Control regimen",
+    "Column 9": "Primary endpoint",
+    "Column 10": "Follow-up duration for primary endpoint(s) in months"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Type of Study": "Follow-up",
+    "Cancer Type": "Melanoma"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Study name",
+    "Column 6": "Name of ICI",
+    "Column 7": "Class of ICI",
+    "Column 8": "Treatment regimen",
+    "Column 9": "Follow-up duration for primary endpoint(s) in months"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Trial Phase": "Phase 3"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Primary endpoint",
+    "Column 6": "Primary multiple, composite, or co-primary endpoints?"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Primary Endpoint": "OS"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Primary endpoint",
+    "Column 6": "Follow-up duration for primary endpoint(s) in months",
+    "Column 7": "Type of follow-up given",
+    "Column 8": "Cancer type"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Primary Endpoint": "PFS"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Follow-up duration for primary endpoint(s) in months"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Type of Therapy": "Immunotherapy"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Number of arms",
+    "Column 6": "Cancer type",
+    "Column 7": "Treatment regimen",
+    "Column 8": "Name of ICI",
+    "Column 9": "Class of ICI",
+    "Column 10": "Control regimen"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)",
+    "Clinical Setting": "Metastatic / Recurrent (Unresectable)"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Name of ICI",
+    "Column 6": "Class of ICI",
+    "Column 7": "Monotherapy/combination",
+    "Column 8": "Lines of treatment"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer Type": "Bladder",
+    "Clinical Setting": "Metastatic / Recurrent (Unresectable)",
+    "Type of Therapy": "Immunotherapy"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Lines of treatment",
+    "Column 6": "ICI Name",
+    "Column 7": "Type of combination (Treatment Arm)",
+    "Column 8": "Control Arm"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer Type": "Head and Neck (HNSCC)",
+    "Type of Therapy": "Immunotherapy",
+    "Year": "2023, 2024"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Primary endpoint",
+    "Column 6": "Name of ICI",
+    "Column 7": "Class of ICI",
+    "Column 8": "Type of combination"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "ICI Name": "Pembrolizumab",
+    "Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)",
+    "Type of Therapy": "Monotherapy",
+    "Control Arm": "Chemo",
+    "Trial Phase": "Phase 3"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Study name"
   }
 }</t>
   </si>
@@ -3016,6 +3317,39 @@
     <t>{
   "selected_filter": {
     "Cancer Type": "Melanoma",
+    "ICI Name": "['Nivolumab', 'Ipilimumab']"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Name of ICI",
+    "Column 6": "Cancer Type",
+    "Column 7": "Treatment regimen"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {},
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Cancer Type",
+    "Column 6": "Trial Phase",
+    "Column 7": "Type of combination (Treatment Arm)",
+    "Column 8": "Control Arm",
+    "Column 9": "Primary Endpoint",
+    "Column 10": "Secondary endpoint"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
     "Type of Study": "Follow-up"
   },
   "selected_column": {
@@ -3023,73 +3357,52 @@
     "Column 2": "PMID",
     "Column 3": "Authors",
     "Column 4": "Year",
+    "Column 5": "Cancer type",
+    "Column 6": "Primary endpoint",
+    "Column 7": "Secondary endpoint",
+    "Column 8": "Type of follow-up given",
+    "Column 9": "Follow-up duration for primary endpoint(s) in months"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Included in MA": "Yes"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
     "Column 5": "Study name",
-    "Column 6": "Primary Endpoint"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Trial Phase": "Phase 3"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Cancer Type",
-    "Column 6": "Primary Endpoint",
-    "Column 7": "Primary multiple, composite, or co-primary endpoints?"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Primary Endpoint": "OS"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Follow-up duration for primary endpoint(s) in months"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Primary Endpoint": "PFS"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Follow-up duration for primary endpoint(s) in months"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {},
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Number of arms",
-    "Column 6": "Cancer Type"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)",
-    "Clinical Setting": "First-line metastatic"
+    "Column 6": "Cancer type",
+    "Column 7": "Treatment regimen",
+    "Column 8": "Control regimen",
+    "Column 9": "Primary endpoint",
+    "Column 10": "Total sample size"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Included in MA": "No"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Study name"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer Type": "Renal Cell Carcinoma (RCC)",
+    "Type of Study": "Original publication"
   },
   "selected_column": {
     "Column 1": "NCT",
@@ -3098,7 +3411,1047 @@
     "Column 4": "Year",
     "Column 5": "ICI Name",
     "Column 6": "Type of combination (Treatment Arm)",
-    "Column 7": "Control Arm"
+    "Column 7": "Control Arm",
+    "Column 8": "Primary Endpoint"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Trial Phase": "Phase 3",
+    "Cancer Type": "Gastric/GEJ",
+    "ICI Class": "PD-L1"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Study name",
+    "Column 6": "Name of ICI",
+    "Column 7": "Treatment regimen",
+    "Column 8": "Control regimen",
+    "Column 9": "Primary endpoint",
+    "Column 10": "Clinical setting in relation to surgery"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "ICI Class": "PD-1",
+    "Cancer Type": "Esophageal/GEJ"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Study name",
+    "Column 6": "Trial phase",
+    "Column 7": "Name of ICI",
+    "Column 8": "Monotherapy/combination",
+    "Column 9": "Treatment regimen",
+    "Column 10": "Primary endpoint"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer Type": "Small Cell Lung Cancer (SCLC)",
+    "Type of Therapy": "Immunotherapy"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Trial Phase",
+    "Column 6": "ICI Name",
+    "Column 7": "ICI Class",
+    "Column 8": "Type of combination (Treatment Arm)",
+    "Column 9": "Primary Endpoint",
+    "Column 10": "Secondary endpoint"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer Type": "Head and Neck (HNSCC)",
+    "Primary Endpoint": "OS"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Treatment regimen",
+    "Column 6": "Control regimen",
+    "Column 7": "Trial phase",
+    "Column 8": "Clinical setting in relation to surgery"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer Type": "Head and Neck (HNSCC)"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "ICI Name",
+    "Column 6": "ICI Class"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer Type": "Breast"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "ICI Name",
+    "Column 6": "ICI Class",
+    "Column 7": "Treatment regimen",
+    "Column 8": "Type of Therapy",
+    "Column 9": "Clinical Setting",
+    "Column 10": "PD-L1 positivity inclusion criteria"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer Type": "Gastric/GEJ",
+    "Clinical Setting": "Second-line+"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "ICI Name",
+    "Column 6": "Type of combination (Treatment Arm)",
+    "Column 7": "Control Arm",
+    "Column 8": "Primary Endpoint",
+    "Column 9": "Is PD-L1 positivity inclusion criteria",
+    "Column 10": "Trial Phase"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer Type": "Hepatocellular carcinoma (HCC)",
+    "Clinical Setting": "Metastatic / Recurrent (Unresectable)",
+    "Type of Therapy": "Immunotherapy"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Lines of treatment",
+    "Column 6": "Name of ICI",
+    "Column 7": "Class of ICI"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer Type": "Renal Cell Carcinoma (RCC)",
+    "Clinical Setting": "Metastatic / Recurrent (Unresectable)",
+    "Type of Therapy": "Immunotherapy"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "ICI Name",
+    "Column 6": "ICI Class",
+    "Column 7": "Type of combination (Treatment Arm)",
+    "Column 8": "Lines of treatment"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Clinical Setting": "Perioperative"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Cancer type",
+    "Column 6": "Treatment regimen",
+    "Column 7": "Name of ICI",
+    "Column 8": "Monotherapy/combination",
+    "Column 9": "Trial phase"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)",
+    "Clinical Setting": "Metastatic / Recurrent (Unresectable)"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Lines of treatment",
+    "Column 6": "Name of ICI",
+    "Column 7": "Monotherapy/combination",
+    "Column 8": "Control regimen",
+    "Column 9": "Trial phase",
+    "Column 10": "Is PD-L1 positivity inclusion criteria"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "ICI Name": "['LAG-3 inhibitor', 'TIGIT inhibitor']"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "ICI Name",
+    "Column 6": "ICI Class",
+    "Column 7": "Cancer Type",
+    "Column 8": "Trial Phase",
+    "Column 9": "Type of combination (Treatment Arm)",
+    "Column 10": "Clinical Setting"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Type of combination (Treatment Arm)": "ICI + MEKi"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Study name",
+    "Column 6": "Cancer type",
+    "Column 7": "Treatment regimen",
+    "Column 8": "Name of ICI",
+    "Column 9": "Trial phase",
+    "Column 10": "Primary endpoint"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "ICI Class",
+    "Column 6": "ICI Name",
+    "Column 7": "Type of combination (Treatment Arm)",
+    "Column 8": "Control Arm",
+    "Column 9": "PD-L1 positivity inclusion criteria"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer Type": "Melanoma"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Monotherapy/combination",
+    "Column 6": "Type of combination",
+    "Column 7": "Treatment regimen"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer Type": "Head and Neck (HNSCC)",
+    "Type of Therapy": "Combination"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Type of combination",
+    "Column 6": "Name of ICI",
+    "Column 7": "Treatment regimen",
+    "Column 8": "Primary endpoint"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)",
+    "Is PD-L1 positivity inclusion criteria": "No"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Name of ICI",
+    "Column 6": "Monotherapy/combination",
+    "Column 7": "Lines of treatment",
+    "Column 8": "Primary endpoint"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Trial Phase": "Phase 3"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Cancer Type"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer Type": "Renal Cell Carcinoma (RCC)",
+    "Type of Therapy": "Combination",
+    "Type of combination (Treatment Arm)": "ICI + TKI"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Type of combination",
+    "Column 6": "Name of ICI",
+    "Column 7": "Treatment regimen",
+    "Column 8": "Control regimen",
+    "Column 9": "Trial phase"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer Type": "Small Cell Lung Cancer (SCLC)",
+    "Type of Therapy": "Combination",
+    "Type of combination (Treatment Arm)": "ICI + Chemo"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Study name",
+    "Column 6": "Treatment regimen",
+    "Column 7": "Name of ICI",
+    "Column 8": "Trial phase"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)",
+    "Type of combination (Treatment Arm)": "ICI + ICI + Chemo"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Study name",
+    "Column 6": "Treatment regimen",
+    "Column 7": "Name of ICI",
+    "Column 8": "Class of ICI"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {},
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Cancer type",
+    "Column 6": "Name of ICI",
+    "Column 7": "Class of ICI",
+    "Column 8": "Trial phase",
+    "Column 9": "Monotherapy/combination"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)",
+    "ICI Name": "['Nivolumab', 'Ipilimumab']"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Type of combination (Treatment Arm)",
+    "Column 6": "ICI Name",
+    "Column 7": "Treatment regimen",
+    "Column 8": "Trial Phase",
+    "Column 9": "Primary Endpoint"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "ICI Class": "['PD-1 inhibitor', 'PD-L1 inhibitor', 'CTLA-4 inhibitor']",
+    "Clinical Setting": "['Third-line', 'Fourth-line', 'Fifth-line', 'Sixth-line', 'Seventh-line', 'Eighth-line', 'Ninth-line', 'Tenth-line']"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Cancer Type",
+    "Column 6": "Treatment regimen",
+    "Column 7": "ICI Name",
+    "Column 8": "ICI Class",
+    "Column 9": "Type of combination (Treatment Arm)",
+    "Column 10": "Clinical Setting"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {},
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Follow-up duration for primary endpoint(s) in months",
+    "Column 6": "Study name"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "ICI Name": "Pembrolizumab",
+    "Cancer Type": "Melanoma",
+    "Clinical Setting": "Adjuvant"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Study name",
+    "Column 6": "Trial phase"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)",
+    "ICI Class": "PD-1"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Treatment regimen",
+    "Column 6": "Name of ICI"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer Type": "Melanoma",
+    "Type of combination (Treatment Arm)": "ICI + ICI"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Name of ICI",
+    "Column 6": "Class of ICI",
+    "Column 7": "Treatment regimen",
+    "Column 8": "Clinical Setting"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "ICI Class": "CTLA-4",
+    "Cancer Type": "Esophageal/GEJ"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Primary endpoint",
+    "Column 6": "Total sample size",
+    "Column 7": "Name of ICI",
+    "Column 8": "Trial phase"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Trial Phase": "Phase 3",
+    "Type of Therapy": "Monotherapy",
+    "Cancer Type": "Urothelial and Bladder"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Study name",
+    "Column 6": "Name of ICI",
+    "Column 7": "Class of ICI",
+    "Column 8": "Primary endpoint",
+    "Column 9": "Follow-up duration for primary endpoint(s) in months"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)",
+    "Clinical Setting": "Adjuvant"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Treatment regimen",
+    "Column 6": "Control regimen",
+    "Column 7": "Name of ICI",
+    "Column 8": "Monotherapy/combination"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "ICI Class": "PD-L1"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "ICI Name",
+    "Column 6": "Cancer Type",
+    "Column 7": "Type of combination (Treatment Arm)",
+    "Column 8": "Control Arm",
+    "Column 9": "Primary Endpoint",
+    "Column 10": "Is PD-L1 positivity inclusion criteria"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Primary Endpoint": "OS"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Cancer type",
+    "Column 6": "Treatment regimen",
+    "Column 7": "Control regimen",
+    "Column 8": "Lines of treatment",
+    "Column 9": "Monotherapy/combination",
+    "Column 10": "Type of combination"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "ICI Class": "PD-1",
+    "Type of Therapy": "Monotherapy"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Cancer type",
+    "Column 6": "Primary endpoint",
+    "Column 7": "Secondary endpoint",
+    "Column 8": "Name of ICI",
+    "Column 9": "Trial phase"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "ICI Class": "PD-L1",
+    "Type of Therapy": "Combination"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Cancer Type",
+    "Column 6": "ICI Name",
+    "Column 7": "Type of combination (Treatment Arm)",
+    "Column 8": "Treatment regimen",
+    "Column 9": "Clinical Setting",
+    "Column 10": "Trial Phase"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer Type": "Head and Neck Cancer",
+    "ICI Class": "['PD-1', 'PD-L1']"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Cancer Type",
+    "Column 6": "ICI Name",
+    "Column 7": "ICI Class",
+    "Column 8": "Type of combination (Treatment Arm)",
+    "Column 9": "Trial Phase"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Trial Phase": "Phase 3",
+    "ICI Name": "Pembrolizumab",
+    "Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Study name"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "ICI Name": "Nivolumab",
+    "Cancer Type": "Melanoma"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Monotherapy/combination",
+    "Column 6": "Type of combination"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "ICI Name": "Atezolizumab",
+    "Cancer Type": "Triple-Negative Breast Cancer",
+    "Type of combination (Treatment Arm)": "ICI + Chemo"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Cancer type",
+    "Column 6": "Name of ICI",
+    "Column 7": "Type of combination",
+    "Column 8": "Treatment regimen",
+    "Column 9": "Is PD-L1 positivity inclusion criteria",
+    "Column 10": "Trial phase"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "ICI Name": "Avelumab",
+    "Cancer Type": "Bladder"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Clinical setting in relation to surgery",
+    "Column 6": "Lines of treatment"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "ICI Name": "Durvalumab",
+    "Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)",
+    "Type of Therapy": "Monotherapy",
+    "Clinical Setting": "Maintenance",
+    "Trial Phase": "Phase 3"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Study name",
+    "Column 6": "Cancer type",
+    "Column 7": "Trial phase",
+    "Column 8": "Treatment regimen",
+    "Column 9": "Control regimen",
+    "Column 10": "Primary endpoint"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "ICI Class": "PD-L1",
+    "Type of Therapy": "Monotherapy"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Cancer Type",
+    "Column 6": "ICI Name"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "ICI Class": "['PD-1', 'CTLA-4']",
+    "Type of Therapy": "Combination",
+    "Type of combination (Treatment Arm)": "ICI + ICI"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Cancer type",
+    "Column 6": "Class of ICI",
+    "Column 7": "Name of ICI",
+    "Column 8": "Trial phase"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Type of combination (Treatment Arm)": "ICI + TKI (Tyrosine Kinase Inhibitor)"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Cancer type",
+    "Column 6": "Name of ICI",
+    "Column 7": "Class of ICI",
+    "Column 8": "Treatment regimen",
+    "Column 9": "Trial phase"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer Type": "Melanoma",
+    "Type of combination (Treatment Arm)": "ICI + BRAFi + MEKi"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Treatment regimen",
+    "Column 6": "ICI Name",
+    "Column 7": "Trial Phase",
+    "Column 8": "Primary Endpoint"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Trial Phase": "Phase 3",
+    "Control Arm": "Placebo"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Cancer Type",
+    "Column 6": "ICI Name",
+    "Column 7": "ICI Class",
+    "Column 8": "Type of combination (Treatment Arm)",
+    "Column 9": "Primary Endpoint"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)",
+    "Control Arm": "Chemo"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Trial phase",
+    "Column 6": "Lines of treatment",
+    "Column 7": "Treatment regimen",
+    "Column 8": "Control regimen"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Control Arm": "Radiation"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Control regimen",
+    "Column 6": "Type of control",
+    "Column 7": "Cancer type",
+    "Column 8": "Trial phase"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Clinical Setting": "Neoadjuvant",
+    "Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Primary endpoint",
+    "Column 6": "Treatment regimen",
+    "Column 7": "Name of ICI",
+    "Column 8": "Monotherapy/combination"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Primary Endpoint": "ORR"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Cancer Type",
+    "Column 6": "Type of Therapy",
+    "Column 7": "Control Arm",
+    "Column 8": "Trial Phase",
+    "Column 9": "Type of combination (Treatment Arm)",
+    "Column 10": "Total sample size"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer Type": "Pancreatic Cancer",
+    "Type of Therapy": "Immunotherapy"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Treatment regimen",
+    "Column 6": "Name of ICI",
+    "Column 7": "Class of ICI",
+    "Column 8": "Monotherapy/combination",
+    "Column 9": "Is PD-L1 positivity inclusion criteria",
+    "Column 10": "Is any other biomarker used for inclusion"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer Type": "Prostate"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Name of ICI",
+    "Column 6": "Class of ICI",
+    "Column 7": "Monotherapy/combination",
+    "Column 8": "Is PD-L1 positivity inclusion criteria",
+    "Column 9": "Is any other biomarker used for inclusion"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer Type": "Multiple Myeloma"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Name of ICI",
+    "Column 6": "Class of ICI",
+    "Column 7": "Primary endpoint"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer Type": "Mesothelioma"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Treatment regimen",
+    "Column 6": "Name of ICI",
+    "Column 7": "Class of ICI",
+    "Column 8": "Type of combination (Treatment Arm)",
+    "Column 9": "Trial Phase"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)",
+    "Type of Study": "Follow-up"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Study name",
+    "Column 6": "Original publication or Follow-up",
+    "Column 7": "Treatment regimen",
+    "Column 8": "Primary endpoint",
+    "Column 9": "Follow-up duration for primary endpoint(s) in months"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Type of Study": "Follow-up",
+    "Cancer Type": "Melanoma"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "ICI Name",
+    "Column 6": "ICI Class",
+    "Column 7": "Type of combination (Treatment Arm)",
+    "Column 8": "Follow-up duration for primary endpoint(s) in months"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Primary Endpoint": "OS"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Cancer type",
+    "Column 6": "Treatment regimen",
+    "Column 7": "Control regimen",
+    "Column 8": "Type of follow-up given",
+    "Column 9": "Follow-up duration for primary endpoint(s) in months"
   }
 }</t>
   </si>
@@ -3106,30 +4459,17 @@
     <t>{
   "selected_filter": {
     "Cancer Type": "Bladder",
-    "Clinical Setting": "Second-line+"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Treatment regimen",
-    "Column 6": "Control Arm",
-    "Column 7": "Primary Endpoint"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer Type": "Head and Neck (HNSCC)"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Primary Endpoint"
+    "Clinical Setting": "Metastatic / Recurrent (Unresectable)",
+    "Type of Therapy": "Immunotherapy"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Lines of treatment",
+    "Column 6": "Name of ICI",
+    "Column 7": "Class of ICI"
   }
 }</t>
   </si>
@@ -3138,44 +4478,57 @@
   "selected_filter": {
     "ICI Name": "Pembrolizumab",
     "Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)",
-    "Control Arm": "Chemo"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "ICI Name": "Nivolumab",
-    "Type of combination (Treatment Arm)": "Combination",
-    "Cancer Type": "Melanoma"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Primary Endpoint": "Quality of Life"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Cancer Type",
-    "Column 6": "Type of Therapy",
-    "Column 7": "Primary Endpoint"
+    "Type of Therapy": "Monotherapy",
+    "Control Arm": "Chemo",
+    "Trial Phase": "Phase 3"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Study name",
+    "Column 6": "Treatment regimen",
+    "Column 7": "Control regimen"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "ICI Name": "Nivolumab, Ipilimumab",
+    "Cancer Type": "Melanoma",
+    "Type of Therapy": "Combination",
+    "Type of combination (Treatment Arm)": "ICI + ICI"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Study name",
+    "Column 6": "Name of ICI",
+    "Column 7": "Cancer type",
+    "Column 8": "Type of combination"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Secondary Endpoint": "Quality of Life"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Secondary endpoint",
+    "Column 6": "Cancer Type",
+    "Column 7": "Trial Phase",
+    "Column 8": "Type of combination (Treatment Arm)",
+    "Column 9": "Control Arm",
+    "Column 10": "Total sample size"
   }
 }</t>
   </si>
@@ -3189,26 +4542,11 @@
     "Column 2": "PMID",
     "Column 3": "Authors",
     "Column 4": "Year",
-    "Column 5": "Cancer Type",
-    "Column 6": "Primary Endpoint",
-    "Column 7": "Type of follow-up given",
-    "Column 8": "Follow-up duration for primary endpoint(s) in months"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Included in MA": "Yes"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Cancer Type",
-    "Column 6": "Primary Endpoint",
-    "Column 7": "Total sample size"
+    "Column 5": "Study name",
+    "Column 6": "Primary endpoint",
+    "Column 7": "Secondary endpoint",
+    "Column 8": "Type of follow-up given",
+    "Column 9": "Follow-up duration for primary endpoint(s) in months"
   }
 }</t>
   </si>
@@ -3222,8 +4560,12 @@
     "Column 2": "PMID",
     "Column 3": "Authors",
     "Column 4": "Year",
-    "Column 5": "Cancer Type",
-    "Column 6": "Primary Endpoint"
+    "Column 5": "Study name",
+    "Column 6": "Cancer type",
+    "Column 7": "Treatment regimen",
+    "Column 8": "Control regimen",
+    "Column 9": "Primary endpoint",
+    "Column 10": "Trial phase"
   }
 }</t>
   </si>
@@ -3238,30 +4580,32 @@
     "Column 2": "PMID",
     "Column 3": "Authors",
     "Column 4": "Year",
+    "Column 5": "Name of ICI",
+    "Column 6": "Class of ICI",
+    "Column 7": "Monotherapy/combination",
+    "Column 8": "Lines of treatment",
+    "Column 9": "Primary endpoint"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Trial Phase": "Phase 3",
+    "Cancer Type": "Gastric/GEJ",
+    "ICI Class": "PD-L1"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
     "Column 5": "Study name",
-    "Column 6": "Treatment regimen",
-    "Column 7": "Primary Endpoint",
-    "Column 8": "Total sample size"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer Type": "Gastric/GEJ",
-    "ICI Class": "PD-L1",
-    "Trial Phase": "Phase 3"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Study name",
-    "Column 6": "Treatment regimen",
-    "Column 7": "Control regimen",
-    "Column 8": "Name of ICI",
-    "Column 9": "Primary Endpoint"
+    "Column 6": "Name of ICI",
+    "Column 7": "Treatment regimen",
+    "Column 8": "Control regimen",
+    "Column 9": "Primary endpoint",
+    "Column 10": "Is PD-L1 positivity inclusion criteria"
   }
 }</t>
   </si>
@@ -3276,16 +4620,39 @@
     "Column 2": "PMID",
     "Column 3": "Authors",
     "Column 4": "Year",
-    "Column 5": "Treatment regimen",
-    "Column 6": "Name of ICI",
-    "Column 7": "Primary Endpoint"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer Type": "Small Cell Lung Cancer (SCLC)"
+    "Column 5": "Study name",
+    "Column 6": "Trial phase",
+    "Column 7": "Name of ICI",
+    "Column 8": "Monotherapy/combination",
+    "Column 9": "Clinical Setting",
+    "Column 10": "Primary endpoint"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer Type": "Small Cell Lung Cancer (SCLC)",
+    "Type of Therapy": "Immunotherapy"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Trial Phase",
+    "Column 6": "ICI Name",
+    "Column 7": "ICI Class",
+    "Column 8": "Type of combination (Treatment Arm)",
+    "Column 9": "Primary Endpoint",
+    "Column 10": "Secondary Endpoint"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer Type": "Head and Neck (HNSCC)"
   },
   "selected_column": {
     "Column 1": "NCT",
@@ -3293,31 +4660,18 @@
     "Column 3": "Authors",
     "Column 4": "Year",
     "Column 5": "ICI Name",
-    "Column 6": "Primary Endpoint"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer Type": "Head and Neck (HNSCC)",
-    "Primary Endpoint": "OS"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Treatment regimen",
-    "Column 6": "Control regimen",
-    "Column 7": "Trial Phase"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer Type": "Head and Neck (HNSCC)"
+    "Column 6": "ICI Class",
+    "Column 7": "Monotherapy/combination",
+    "Column 8": "Type of combination (Treatment Arm)",
+    "Column 9": "Treatment regimen",
+    "Column 10": "Trial Phase"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer Type": "Breast"
   },
   "selected_column": {
     "Column 1": "NCT",
@@ -3332,22 +4686,7 @@
   <si>
     <t>{
   "selected_filter": {
-    "Cancer Type": "Breast"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "ICI Name",
-    "Column 6": "ICI Class"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer Type": "Gastric/GEJ",
+    "Cancer Type": "Hepatocellular carcinoma (HCC)",
     "Clinical Setting": "Metastatic / Recurrent (Unresectable)"
   },
   "selected_column": {
@@ -3355,23 +4694,12 @@
     "Column 2": "PMID",
     "Column 3": "Authors",
     "Column 4": "Year",
-    "Column 5": "Lines of treatment"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer Type": "Hepatocellular carcinoma (HCC)",
-    "Clinical Setting": "First-line metastatic"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Treatment regimen",
-    "Column 6": "Lines of treatment"
+    "Column 5": "Lines of treatment",
+    "Column 6": "Name of ICI",
+    "Column 7": "Class of ICI",
+    "Column 8": "Monotherapy/combination",
+    "Column 9": "Treatment regimen",
+    "Column 10": "Control regimen"
   }
 }</t>
   </si>
@@ -3386,16 +4714,90 @@
     "Column 2": "PMID",
     "Column 3": "Authors",
     "Column 4": "Year",
-    "Column 5": "Type of Therapy",
+    "Column 5": "ICI Name",
+    "Column 6": "ICI Class",
+    "Column 7": "Type of combination (Treatment Arm)",
+    "Column 8": "Lines of treatment"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)",
+    "Clinical Setting": "Metastatic / Recurrent (Unresectable)",
+    "Type of Therapy": "Immunotherapy"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Lines of treatment",
+    "Column 6": "Name of ICI",
+    "Column 7": "Class of ICI",
+    "Column 8": "Monotherapy/combination",
+    "Column 9": "Primary endpoint"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "ICI Name": "['LAG-3', 'TIGIT']"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Name of ICI",
+    "Column 6": "Class of ICI",
+    "Column 7": "Cancer type",
+    "Column 8": "Treatment regimen",
+    "Column 9": "Monotherapy/combination",
+    "Column 10": "Trial phase"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "ICI Class",
+    "Column 6": "ICI Name",
+    "Column 7": "Type of combination (Treatment Arm)",
+    "Column 8": "Control Arm"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer Type": "Melanoma"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Type of combination (Treatment Arm)",
     "Column 6": "Treatment regimen",
-    "Column 7": "Clinical Setting"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Clinical Setting": "Perioperative"
+    "Column 7": "Trial Phase"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer Type": "Head and Neck (HNSCC)",
+    "Type of Therapy": "Combination"
   },
   "selected_column": {
     "Column 1": "NCT",
@@ -3403,17 +4805,18 @@
     "Column 3": "Authors",
     "Column 4": "Year",
     "Column 5": "Cancer Type",
-    "Column 6": "Type of Therapy",
-    "Column 7": "Type of combination (Treatment Arm)",
-    "Column 8": "Primary Endpoint"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)",
-    "Clinical Setting": "Second-line+"
+    "Column 6": "Type of combination (Treatment Arm)",
+    "Column 7": "ICI Name",
+    "Column 8": "Treatment regimen",
+    "Column 9": "Primary Endpoint"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer Type": "Renal Cell Carcinoma (RCC)",
+    "Type of combination (Treatment Arm)": "ICI + TKI"
   },
   "selected_column": {
     "Column 1": "NCT",
@@ -3423,14 +4826,679 @@
     "Column 5": "Treatment regimen",
     "Column 6": "Name of ICI",
     "Column 7": "Control regimen",
-    "Column 8": "Primary Endpoint"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "ICI Class": "LAG-3 inhibitor OR TIGIT inhibitor"
+    "Column 8": "Trial phase",
+    "Column 9": "Lines of treatment",
+    "Column 10": "Primary endpoint"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer Type": "Small Cell Lung Cancer (SCLC)",
+    "Type of combination (Treatment Arm)": "ICI + Chemo",
+    "ICI Class": "PD-L1"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Cancer type",
+    "Column 6": "Type of combination",
+    "Column 7": "Class of ICI",
+    "Column 8": "Name of ICI",
+    "Column 9": "Treatment regimen",
+    "Column 10": "Control regimen"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)",
+    "Type of combination (Treatment Arm)": "ICI + ICI + Chemo"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Treatment regimen",
+    "Column 6": "Name of ICI",
+    "Column 7": "Class of ICI",
+    "Column 8": "Trial phase"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Year": "['2010', '2011', '2012']"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Cancer Type",
+    "Column 6": "ICI Name",
+    "Column 7": "ICI Class",
+    "Column 8": "Original publication or Follow-up"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)",
+    "Type of combination (Treatment Arm)": "ICI + ICI",
+    "ICI Name": "['Nivolumab', 'Ipilimumab']"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Cancer Type",
+    "Column 6": "ICI Name",
+    "Column 7": "Treatment regimen",
+    "Column 8": "Trial Phase"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Clinical Setting": "Metastatic / Recurrent (Unresectable)"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Cancer type",
+    "Column 6": "Lines of treatment",
+    "Column 7": "Name of ICI",
+    "Column 8": "Treatment regimen",
+    "Column 9": "Control regimen",
+    "Column 10": "Primary endpoint"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Type of Study": "Follow-up"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Study name",
+    "Column 6": "Follow-up duration for primary endpoint(s) in months"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer Type": "Melanoma",
+    "Type of combination (Treatment Arm)": "ICI + ICI"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Treatment regimen",
+    "Column 6": "Clinical setting in relation to surgery"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Trial Phase": "Phase 3",
+    "Type of Therapy": "Monotherapy",
+    "Cancer Type": "Urothelial and Bladder"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Follow-up duration for primary endpoint(s) in months",
+    "Column 6": "Name of ICI",
+    "Column 7": "Primary endpoint"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "ICI Class": "PD-1",
+    "Type of Therapy": "Monotherapy"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Cancer type",
+    "Column 6": "Name of ICI",
+    "Column 7": "Primary endpoint",
+    "Column 8": "Secondary endpoint"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "ICI Class": "CTLA-4",
+    "Type of Therapy": "Monotherapy"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Class of ICI",
+    "Column 6": "Monotherapy/combination",
+    "Column 7": "Cancer type",
+    "Column 8": "Name of ICI",
+    "Column 9": "Trial phase"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "ICI Class": "CTLA-4",
+    "Type of Therapy": "Combination"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "ICI Name",
+    "Column 6": "Type of combination (Treatment Arm)",
+    "Column 7": "Treatment regimen",
+    "Column 8": "Cancer Type",
+    "Column 9": "Clinical Setting",
+    "Column 10": "Primary Endpoint"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer Type": "Head and Neck (HNSCC)"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "ICI Class",
+    "Column 6": "ICI Name",
+    "Column 7": "Type of combination (Treatment Arm)",
+    "Column 8": "Control Arm",
+    "Column 9": "Trial Phase",
+    "Column 10": "Is PD-L1 positivity inclusion criteria"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "ICI Name": "Nivolumab",
+    "Cancer Type": "Melanoma"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Type of Therapy",
+    "Column 6": "Trial Phase",
+    "Column 7": "Treatment Arm",
+    "Column 8": "Control Arm",
+    "Column 9": "Primary Endpoint"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "ICI Class": "PD-L1",
+    "Type of Therapy": "Monotherapy"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Cancer type",
+    "Column 6": "Name of ICI",
+    "Column 7": "Treatment regimen"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "ICI Class": "['PD-1', 'CTLA-4']",
+    "Type of Therapy": "Combination",
+    "Type of combination (Treatment Arm)": "ICI + ICI"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Cancer type",
+    "Column 6": "Name of ICI",
+    "Column 7": "Trial phase"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)",
+    "Type of Therapy": "Combination",
+    "Type of combination (Treatment Arm)": "ICI + Chemo"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Primary endpoint"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Type of combination (Treatment Arm)": "ICI + Radiation"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Cancer type",
+    "Column 6": "Treatment regimen",
+    "Column 7": "Name of ICI",
+    "Column 8": "Trial phase",
+    "Column 9": "Primary endpoint"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Type of combination (Treatment Arm)": "ICI + Chemo + Anti-VEGF"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Cancer type",
+    "Column 6": "Treatment regimen",
+    "Column 7": "Name of ICI",
+    "Column 8": "Lines of treatment",
+    "Column 9": "Clinical setting in relation to surgery"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Type of combination (Treatment Arm)": "ICI + ICI + Chemo"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Name of ICI",
+    "Column 6": "Class of ICI",
+    "Column 7": "Treatment regimen",
+    "Column 8": "Cancer type",
+    "Column 9": "Trial phase"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Trial Phase": "Phase 3",
+    "Control Arm": "Placebo"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Cancer Type",
+    "Column 6": "ICI Name",
+    "Column 7": "ICI Class",
+    "Column 8": "Type of Therapy",
+    "Column 9": "Primary Endpoint"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Control Arm": "Chemo / Anti-EGFR"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Cancer type",
+    "Column 6": "Trial phase",
+    "Column 7": "Treatment regimen",
+    "Column 8": "Name of ICI",
+    "Column 9": "Control regimen",
+    "Column 10": "Primary endpoint"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Control Arm": "Radiation"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Control regimen",
+    "Column 6": "Type of control",
+    "Column 7": "Cancer type",
+    "Column 8": "Trial phase",
+    "Column 9": "Study name"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Clinical Setting": "Adjuvant",
+    "Cancer Type": "Melanoma"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "ICI Name",
+    "Column 6": "ICI Class",
+    "Column 7": "Type of combination (Treatment Arm)",
+    "Column 8": "Control Arm",
+    "Column 9": "Primary Endpoint",
+    "Column 10": "Trial Phase"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Primary Endpoint": "Path CR"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Primary endpoint",
+    "Column 6": "Clinical setting in relation to surgery",
+    "Column 7": "Cancer type",
+    "Column 8": "Treatment regimen",
+    "Column 9": "Control regimen",
+    "Column 10": "Trial phase"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Primary Endpoint": "Safety"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Primary endpoint",
+    "Column 6": "Trial phase",
+    "Column 7": "Cancer type",
+    "Column 8": "Treatment regimen",
+    "Column 9": "Total sample size"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Is PD-L1 positivity inclusion criteria"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer Type": "Mesothelioma"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Treatment regimen",
+    "Column 6": "Class of ICI",
+    "Column 7": "Type of combination"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Type of Study": "Follow-up",
+    "Cancer Type": "Melanoma",
+    "Type of Therapy": "Immunotherapy"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Study name",
+    "Column 6": "Name of ICI",
+    "Column 7": "Class of ICI",
+    "Column 8": "Treatment regimen",
+    "Column 9": "Follow-up duration for primary endpoint(s) in months"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Trial Phase": "Phase 3"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Trial phase",
+    "Column 6": "Primary endpoint",
+    "Column 7": "Primary multiple, composite, or co-primary endpoints?"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Type of Therapy": "Immunotherapy"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Number of arms",
+    "Column 6": "Name of ICI",
+    "Column 7": "Class of ICI",
+    "Column 8": "Treatment regimen",
+    "Column 9": "Control regimen"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer Type": "Head and Neck (HNSCC)",
+    "Type of Therapy": "Immunotherapy"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Primary Endpoint",
+    "Column 6": "ICI Name",
+    "Column 7": "ICI Class"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer Type": "Melanoma",
+    "ICI Name": "['Nivolumab', 'Ipilimumab']",
+    "Type of combination (Treatment Arm)": "ICI + ICI"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "ICI Name"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {},
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Secondary endpoint",
+    "Column 6": "Cancer type",
+    "Column 7": "Trial phase",
+    "Column 8": "Treatment regimen",
+    "Column 9": "Control regimen",
+    "Column 10": "Total sample size"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer Type": "Head and Neck (HNSCC)"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "ICI Name",
+    "Column 6": "ICI Class",
+    "Column 7": "Type of combination (Treatment Arm)",
+    "Column 8": "Trial Phase"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer Type": "Breast"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Name of ICI",
+    "Column 6": "Class of ICI",
+    "Column 7": "Treatment regimen",
+    "Column 8": "Monotherapy/combination",
+    "Column 9": "Type of combination"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer Type": "Gastric/GEJ",
+    "Clinical Setting": "Metastatic / Recurrent (Unresectable)",
+    "ICI Class": "PD-1/PD-L1 inhibitor"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Name of ICI",
+    "Column 6": "Lines of treatment",
+    "Column 7": "Treatment regimen",
+    "Column 8": "Control regimen",
+    "Column 9": "Primary endpoint",
+    "Column 10": "Is PD-L1 positivity inclusion criteria"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "ICI Name": "['LAG-3 inhibitor', 'TIGIT inhibitor']"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Cancer Type",
+    "Column 6": "ICI Name",
+    "Column 7": "Treatment regimen",
+    "Column 8": "Trial Phase"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Trial Phase": "Phase 3"
   },
   "selected_column": {
     "Column 1": "NCT",
@@ -3446,122 +5514,8 @@
   <si>
     <t>{
   "selected_filter": {
-    "Type of combination (Treatment Arm)": "ICI + MEKi"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Cancer Type",
-    "Column 6": "Type of combination (Treatment Arm)",
-    "Column 7": "ICI Name"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)",
-    "ICI Class": "PD-L1"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Name of ICI",
-    "Column 6": "Treatment regimen",
-    "Column 7": "Control regimen",
-    "Column 8": "Primary endpoint"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer Type": "Melanoma"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Type of Therapy",
-    "Column 6": "Type of combination (Treatment Arm)"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer Type": "Head and Neck (HNSCC)",
-    "Type of Therapy": "Combination"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Treatment regimen",
-    "Column 6": "Type of combination (Treatment Arm)",
-    "Column 7": "ICI Name"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Treatment regimen",
-    "Column 6": "Primary Endpoint",
-    "Column 7": "Is PD-L1 positivity inclusion criteria"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Trial Phase": "Phase 3",
-    "Type of Therapy": "ICI"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Cancer Type"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer Type": "Renal Cell Carcinoma (RCC)",
-    "Type of combination (Treatment Arm)": "ICI + Targeted therapy"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Type of Therapy",
-    "Column 6": "ICI Name",
-    "Column 7": "Primary Endpoint",
-    "Column 8": "Trial Phase"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
     "Cancer Type": "Small Cell Lung Cancer (SCLC)",
+    "Type of Therapy": "Combination",
     "Type of combination (Treatment Arm)": "ICI + Chemo"
   },
   "selected_column": {
@@ -3569,10 +5523,10 @@
     "Column 2": "PMID",
     "Column 3": "Authors",
     "Column 4": "Year",
-    "Column 5": "Type of Therapy",
-    "Column 6": "ICI Name",
-    "Column 7": "Trial Phase",
-    "Column 8": "Primary Endpoint"
+    "Column 5": "Study name",
+    "Column 6": "Trial phase",
+    "Column 7": "Treatment regimen",
+    "Column 8": "Name of ICI"
   }
 }</t>
   </si>
@@ -3587,908 +5541,19 @@
     "Column 2": "PMID",
     "Column 3": "Authors",
     "Column 4": "Year",
-    "Column 5": "Trial Phase",
-    "Column 6": "Primary Endpoint"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Year": "2010-2012"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Cancer Type"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "ICI Name": "Nivolumab",
-    "Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)",
-    "Type of combination (Treatment Arm)": "ICI + ICI"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Primary Endpoint",
-    "Column 6": "Trial Phase"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Clinical Setting": "Metastatic / Recurrent (Unresectable)"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Cancer Type",
-    "Column 6": "Type of Therapy",
-    "Column 7": "Type of combination (Treatment Arm)"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {},
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Cancer Type",
-    "Column 6": "Follow-up duration for primary endpoint(s) in months"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "ICI Name": "Pembrolizumab",
-    "Clinical Setting": "Adjuvant",
-    "Cancer Type": "Melanoma"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "ICI Class": "CTLA-4",
-    "Cancer Type": "Gastric/GEJ"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Total sample size",
-    "Column 6": "Primary endpoint"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "ICI Class": "CTLA-4",
-    "Type of Therapy": "Combination"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Cancer Type",
-    "Column 6": "Type of combination (Treatment Arm)",
-    "Column 7": "Primary Endpoint",
-    "Column 8": "Total sample size"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Type of combination (Treatment Arm)": "ICI + ICI",
-    "ICI Class": "PD-1/PD-L1 + CTLA-4"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Cancer Type"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer Type": "Melanoma",
-    "Type of combination (Treatment Arm)": "ICI + BRAFi + MEKi"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Treatment regimen",
-    "Column 6": "Primary Endpoint"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Type of combination (Treatment Arm)": "ICI + Anti-VEGF"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Cancer Type",
-    "Column 6": "Type of Therapy",
-    "Column 7": "ICI Name",
-    "Column 8": "Primary Endpoint"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)",
-    "Control Arm": "Chemo"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Control Arm",
-    "Column 6": "Treatment regimen",
-    "Column 7": "Trial Phase",
-    "Column 8": "Total sample size"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer Type": "Hepatocellular carcinoma (HCC)",
-    "Control Arm": "TKI (Tyrosine Kinase Inhibitor)"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Control Arm",
-    "Column 6": "Primary Endpoint"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Control Arm": "Chemo / Anti-EGFR"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Cancer Type",
-    "Column 6": "Type of Therapy",
-    "Column 7": "Treatment regimen",
-    "Column 8": "Control Arm",
-    "Column 9": "Primary Endpoint"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Primary Endpoint": "Safety"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Cancer Type",
-    "Column 6": "Primary Endpoint"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Treatment regimen",
-    "Column 6": "Is PD-L1 positivity inclusion criteria"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer Type": "Colorectal",
-    "Included in MA": "MSI-H/dMMR"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "ICI Name",
-    "Column 6": "Type of Therapy"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer Type": "Prostate"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Type of Therapy",
-    "Column 6": "ICI Name",
-    "Column 7": "Included in MA"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)",
-    "Type of Study": "Follow-up"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Follow-up duration for primary endpoint(s) in months",
-    "Column 6": "Primary Endpoint"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer Type": "Melanoma",
-    "Type of Study": "Follow-up"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Study name",
-    "Column 6": "Primary Endpoint",
-    "Column 7": "Follow-up duration for primary endpoint(s) in months"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Primary Endpoint": "OS"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Cancer Type",
-    "Column 6": "Follow-up duration for primary endpoint(s) in months"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)",
-    "Clinical Setting": "First-line metastatic"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "ICI Name",
-    "Column 6": "ICI Class",
-    "Column 7": "Type of combination (Treatment Arm)",
-    "Column 8": "Control Arm"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer Type": "Bladder",
-    "Clinical Setting": "Second-line+"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Type of Therapy",
-    "Column 6": "ICI Name",
-    "Column 7": "Primary Endpoint"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer Type": "Melanoma",
-    "ICI Name": "Nivolumab",
-    "Type of combination (Treatment Arm)": "Nivolumab + Ipilimumab"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Primary Endpoint": "Quality of Life"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Cancer Type",
-    "Column 6": "Trial Phase"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Type of Study": "Follow-up"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Cancer Type",
-    "Column 6": "Primary Endpoint",
-    "Column 7": "Type of follow-up given"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Included in MA": "Yes"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Cancer Type",
-    "Column 6": "Primary Endpoint"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Included in MA": "No"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Cancer Type"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "ICI Class": "PD-1",
-    "Cancer Type": "Esophageal/GEJ"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Treatment regimen",
-    "Column 6": "Name of ICI",
-    "Column 7": "Primary endpoint"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer Type": "Hepatocellular carcinoma (HCC)",
-    "Clinical Setting": "First-line metastatic"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Lines of treatment",
-    "Column 6": "Treatment regimen",
-    "Column 7": "Control regimen",
-    "Column 8": "Primary Endpoint"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer Type": "Renal Cell Carcinoma (RCC)",
-    "Clinical Setting": "Metastatic / Recurrent (Unresectable)"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Treatment regimen",
-    "Column 6": "Lines of treatment"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Clinical Setting": "Perioperative"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Cancer Type",
-    "Column 6": "Type of Therapy",
-    "Column 7": "Primary Endpoint"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)",
-    "ICI Class": "PD-L1"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Name of ICI",
-    "Column 6": "Treatment regimen",
-    "Column 7": "Control Arm",
-    "Column 8": "Primary Endpoint"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer Type": "Renal Cell Carcinoma (RCC)",
-    "Type of combination (Treatment Arm)": "ICI + TKI (Tyrosine Kinase Inhibitor)"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Primary Endpoint",
-    "Column 6": "Total sample size"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)",
-    "Type of combination (Treatment Arm)": "ICI + ICI"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Treatment regimen",
-    "Column 6": "Primary Endpoint",
-    "Column 7": "Trial Phase"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Clinical Setting": "≥3L"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Cancer Type",
-    "Column 6": "Type of Therapy",
-    "Column 7": "ICI Name",
-    "Column 8": "Primary Endpoint"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "ICI Class": "PD-L1"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Cancer Type",
-    "Column 6": "Type of Therapy",
-    "Column 7": "ICI Name",
-    "Column 8": "Primary Endpoint"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {},
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Study name"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "ICI Class": "CTLA-4",
-    "Type of Therapy": "Combination"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Cancer Type",
-    "Column 6": "Treatment regimen",
-    "Column 7": "Primary Endpoint"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "ICI Name": "Pembrolizumab",
-    "Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)",
-    "Trial Phase": "Phase 3"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Primary Endpoint"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "ICI Name": "Atezolizumab",
-    "Type of combination (Treatment Arm)": "ICI + Chemo",
-    "Cancer Type": "Breast"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Cancer Type",
-    "Column 6": "Treatment regimen",
-    "Column 7": "Is PD-L1 positivity inclusion criteria",
-    "Column 8": "Primary Endpoint"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Trial Phase": "Phase 3",
-    "Control Arm": "Placebo"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Cancer Type",
-    "Column 6": "Primary Endpoint"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer Type": "Hepatocellular carcinoma (HCC)",
-    "Control Arm": "TKI (Tyrosine Kinase Inhibitor)"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Control Arm",
-    "Column 6": "Primary Endpoint",
-    "Column 7": "Trial Phase"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Control Arm": "Interferon"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Cancer Type",
-    "Column 6": "Trial Phase",
-    "Column 7": "Primary Endpoint"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Clinical Setting": "Adjuvant",
-    "Cancer Type": "Melanoma"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Type of Therapy",
-    "Column 6": "ICI Name",
-    "Column 7": "Control Arm",
-    "Column 8": "Primary Endpoint"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Primary Endpoint": "ORR"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Cancer Type",
-    "Column 6": "Treatment regimen",
-    "Column 7": "Control regimen",
-    "Column 8": "Trial Phase"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Primary Endpoint": "PFS (Progression-Free Survival)"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Cancer Type",
-    "Column 6": "Trial Phase"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Primary Endpoint": "RFS (Recurrence-/Relapse-Free Survival)"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Cancer Type",
-    "Column 6": "Type of Therapy",
-    "Column 7": "Primary Endpoint",
-    "Column 8": "Total sample size"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer Type": "Colorectal",
-    "Is any other biomarker used for inclusion": "MSI-H/dMMR"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "ICI Name",
-    "Column 6": "Type of Therapy"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer Type": "Mesothelioma"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Type of Therapy",
-    "Column 6": "Type of combination (Treatment Arm)"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {},
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Cancer Type",
-    "Column 6": "Type of Therapy",
-    "Column 7": "Type of combination (Treatment Arm)",
-    "Column 8": "Control Arm"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)",
-    "ICI Name": "Pembrolizumab",
-    "Control Arm": "Chemo"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer Type": "Gastric/GEJ",
-    "ICI Class": "PD-L1",
-    "Trial Phase": "Phase 3"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
     "Column 5": "Study name",
     "Column 6": "Treatment regimen",
-    "Column 7": "Control regimen",
-    "Column 8": "Primary endpoint"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer Type": "Hepatocellular carcinoma (HCC)",
-    "Clinical Setting": "First-line metastatic"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Clinical Setting",
-    "Column 6": "Type of Therapy",
-    "Column 7": "Treatment regimen",
-    "Column 8": "Primary Endpoint"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer Type": "Head and Neck (HNSCC)",
-    "Type of Therapy": "Combination"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Treatment regimen",
-    "Column 6": "Type of combination (Treatment Arm)"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Treatment regimen",
-    "Column 6": "Is PD-L1 positivity inclusion criteria",
-    "Column 7": "Primary Endpoint",
-    "Column 8": "Trial Phase"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Trial Phase": "Phase 3",
-    "Type of Therapy": "ICI"
+    "Column 7": "Name of ICI",
+    "Column 8": "Class of ICI",
+    "Column 9": "Primary endpoint",
+    "Column 10": "Lines of treatment"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Type of Study": "Original publication"
   },
   "selected_column": {
     "Column 1": "NCT",
@@ -4496,23 +5561,23 @@
     "Column 3": "Authors",
     "Column 4": "Year",
     "Column 5": "Cancer Type",
-    "Column 6": "Primary Endpoint"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)",
-    "Type of combination (Treatment Arm)": "ICI + ICI + Chemo"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Treatment regimen",
-    "Column 6": "Primary Endpoint"
+    "Column 6": "ICI Name",
+    "Column 7": "ICI Class"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {},
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Study name",
+    "Column 6": "Cancer type",
+    "Column 7": "Type of follow-up given",
+    "Column 8": "Follow-up duration for primary endpoint(s) in months"
   }
 }</t>
   </si>
@@ -4903,10 +5968,10 @@
         <v>205</v>
       </c>
       <c r="D2" t="s">
-        <v>205</v>
+        <v>305</v>
       </c>
       <c r="E2" t="s">
-        <v>205</v>
+        <v>305</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -4920,10 +5985,10 @@
         <v>206</v>
       </c>
       <c r="D3" t="s">
-        <v>206</v>
+        <v>306</v>
       </c>
       <c r="E3" t="s">
-        <v>206</v>
+        <v>362</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -4937,10 +6002,10 @@
         <v>207</v>
       </c>
       <c r="D4" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="E4" t="s">
-        <v>207</v>
+        <v>307</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -4954,10 +6019,10 @@
         <v>208</v>
       </c>
       <c r="D5" t="s">
-        <v>208</v>
+        <v>308</v>
       </c>
       <c r="E5" t="s">
-        <v>208</v>
+        <v>363</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -4971,7 +6036,7 @@
         <v>209</v>
       </c>
       <c r="D6" t="s">
-        <v>209</v>
+        <v>309</v>
       </c>
       <c r="E6" t="s">
         <v>209</v>
@@ -5005,10 +6070,10 @@
         <v>211</v>
       </c>
       <c r="D8" t="s">
+        <v>310</v>
+      </c>
+      <c r="E8" t="s">
         <v>211</v>
-      </c>
-      <c r="E8" t="s">
-        <v>335</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -5039,10 +6104,10 @@
         <v>213</v>
       </c>
       <c r="D10" t="s">
-        <v>213</v>
+        <v>311</v>
       </c>
       <c r="E10" t="s">
-        <v>213</v>
+        <v>311</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -5059,7 +6124,7 @@
         <v>214</v>
       </c>
       <c r="E11" t="s">
-        <v>336</v>
+        <v>214</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -5073,10 +6138,10 @@
         <v>215</v>
       </c>
       <c r="D12" t="s">
-        <v>215</v>
+        <v>312</v>
       </c>
       <c r="E12" t="s">
-        <v>215</v>
+        <v>364</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -5090,10 +6155,10 @@
         <v>216</v>
       </c>
       <c r="D13" t="s">
-        <v>216</v>
+        <v>313</v>
       </c>
       <c r="E13" t="s">
-        <v>216</v>
+        <v>313</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -5110,7 +6175,7 @@
         <v>217</v>
       </c>
       <c r="E14" t="s">
-        <v>217</v>
+        <v>365</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -5124,10 +6189,10 @@
         <v>218</v>
       </c>
       <c r="D15" t="s">
-        <v>306</v>
+        <v>218</v>
       </c>
       <c r="E15" t="s">
-        <v>337</v>
+        <v>366</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -5141,10 +6206,10 @@
         <v>219</v>
       </c>
       <c r="D16" t="s">
-        <v>219</v>
+        <v>314</v>
       </c>
       <c r="E16" t="s">
-        <v>219</v>
+        <v>367</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -5158,10 +6223,10 @@
         <v>220</v>
       </c>
       <c r="D17" t="s">
-        <v>220</v>
+        <v>315</v>
       </c>
       <c r="E17" t="s">
-        <v>338</v>
+        <v>315</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -5175,10 +6240,10 @@
         <v>221</v>
       </c>
       <c r="D18" t="s">
-        <v>221</v>
+        <v>316</v>
       </c>
       <c r="E18" t="s">
-        <v>221</v>
+        <v>368</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -5192,10 +6257,10 @@
         <v>222</v>
       </c>
       <c r="D19" t="s">
-        <v>222</v>
+        <v>317</v>
       </c>
       <c r="E19" t="s">
-        <v>339</v>
+        <v>317</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -5209,10 +6274,10 @@
         <v>223</v>
       </c>
       <c r="D20" t="s">
-        <v>223</v>
+        <v>318</v>
       </c>
       <c r="E20" t="s">
-        <v>223</v>
+        <v>318</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -5243,10 +6308,10 @@
         <v>225</v>
       </c>
       <c r="D22" t="s">
-        <v>225</v>
+        <v>319</v>
       </c>
       <c r="E22" t="s">
-        <v>225</v>
+        <v>319</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -5277,10 +6342,10 @@
         <v>227</v>
       </c>
       <c r="D24" t="s">
-        <v>227</v>
+        <v>320</v>
       </c>
       <c r="E24" t="s">
-        <v>227</v>
+        <v>369</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -5294,10 +6359,10 @@
         <v>228</v>
       </c>
       <c r="D25" t="s">
-        <v>307</v>
+        <v>321</v>
       </c>
       <c r="E25" t="s">
-        <v>307</v>
+        <v>370</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -5314,7 +6379,7 @@
         <v>229</v>
       </c>
       <c r="E26" t="s">
-        <v>229</v>
+        <v>371</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -5328,7 +6393,7 @@
         <v>230</v>
       </c>
       <c r="D27" t="s">
-        <v>230</v>
+        <v>322</v>
       </c>
       <c r="E27" t="s">
         <v>230</v>
@@ -5348,7 +6413,7 @@
         <v>231</v>
       </c>
       <c r="E28" t="s">
-        <v>231</v>
+        <v>372</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -5379,7 +6444,7 @@
         <v>233</v>
       </c>
       <c r="D30" t="s">
-        <v>308</v>
+        <v>323</v>
       </c>
       <c r="E30" t="s">
         <v>233</v>
@@ -5396,7 +6461,7 @@
         <v>234</v>
       </c>
       <c r="D31" t="s">
-        <v>309</v>
+        <v>234</v>
       </c>
       <c r="E31" t="s">
         <v>234</v>
@@ -5416,7 +6481,7 @@
         <v>235</v>
       </c>
       <c r="E32" t="s">
-        <v>235</v>
+        <v>373</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -5433,7 +6498,7 @@
         <v>236</v>
       </c>
       <c r="E33" t="s">
-        <v>236</v>
+        <v>374</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -5447,10 +6512,10 @@
         <v>237</v>
       </c>
       <c r="D34" t="s">
-        <v>237</v>
+        <v>324</v>
       </c>
       <c r="E34" t="s">
-        <v>340</v>
+        <v>375</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -5464,7 +6529,7 @@
         <v>238</v>
       </c>
       <c r="D35" t="s">
-        <v>310</v>
+        <v>325</v>
       </c>
       <c r="E35" t="s">
         <v>238</v>
@@ -5481,10 +6546,10 @@
         <v>239</v>
       </c>
       <c r="D36" t="s">
-        <v>311</v>
+        <v>239</v>
       </c>
       <c r="E36" t="s">
-        <v>341</v>
+        <v>239</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -5501,7 +6566,7 @@
         <v>240</v>
       </c>
       <c r="E37" t="s">
-        <v>342</v>
+        <v>240</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -5532,10 +6597,10 @@
         <v>242</v>
       </c>
       <c r="D39" t="s">
-        <v>312</v>
+        <v>242</v>
       </c>
       <c r="E39" t="s">
-        <v>312</v>
+        <v>376</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -5617,10 +6682,10 @@
         <v>247</v>
       </c>
       <c r="D44" t="s">
-        <v>247</v>
+        <v>326</v>
       </c>
       <c r="E44" t="s">
-        <v>247</v>
+        <v>377</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -5637,7 +6702,7 @@
         <v>248</v>
       </c>
       <c r="E45" t="s">
-        <v>343</v>
+        <v>378</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -5651,7 +6716,7 @@
         <v>249</v>
       </c>
       <c r="D46" t="s">
-        <v>249</v>
+        <v>327</v>
       </c>
       <c r="E46" t="s">
         <v>249</v>
@@ -5671,7 +6736,7 @@
         <v>250</v>
       </c>
       <c r="E47" t="s">
-        <v>250</v>
+        <v>379</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -5685,10 +6750,10 @@
         <v>251</v>
       </c>
       <c r="D48" t="s">
-        <v>251</v>
+        <v>328</v>
       </c>
       <c r="E48" t="s">
-        <v>344</v>
+        <v>328</v>
       </c>
     </row>
     <row r="49" spans="1:5">
@@ -5722,7 +6787,7 @@
         <v>253</v>
       </c>
       <c r="E50" t="s">
-        <v>345</v>
+        <v>253</v>
       </c>
     </row>
     <row r="51" spans="1:5">
@@ -5739,7 +6804,7 @@
         <v>254</v>
       </c>
       <c r="E51" t="s">
-        <v>346</v>
+        <v>254</v>
       </c>
     </row>
     <row r="52" spans="1:5">
@@ -5770,10 +6835,10 @@
         <v>256</v>
       </c>
       <c r="D53" t="s">
-        <v>313</v>
+        <v>256</v>
       </c>
       <c r="E53" t="s">
-        <v>256</v>
+        <v>380</v>
       </c>
     </row>
     <row r="54" spans="1:5">
@@ -5787,10 +6852,10 @@
         <v>257</v>
       </c>
       <c r="D54" t="s">
-        <v>314</v>
+        <v>257</v>
       </c>
       <c r="E54" t="s">
-        <v>314</v>
+        <v>381</v>
       </c>
     </row>
     <row r="55" spans="1:5">
@@ -5804,10 +6869,10 @@
         <v>258</v>
       </c>
       <c r="D55" t="s">
-        <v>315</v>
+        <v>258</v>
       </c>
       <c r="E55" t="s">
-        <v>347</v>
+        <v>258</v>
       </c>
     </row>
     <row r="56" spans="1:5">
@@ -5821,10 +6886,10 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>259</v>
+        <v>329</v>
       </c>
       <c r="E56" t="s">
-        <v>259</v>
+        <v>329</v>
       </c>
     </row>
     <row r="57" spans="1:5">
@@ -5838,7 +6903,7 @@
         <v>260</v>
       </c>
       <c r="D57" t="s">
-        <v>316</v>
+        <v>330</v>
       </c>
       <c r="E57" t="s">
         <v>260</v>
@@ -5855,7 +6920,7 @@
         <v>261</v>
       </c>
       <c r="D58" t="s">
-        <v>261</v>
+        <v>331</v>
       </c>
       <c r="E58" t="s">
         <v>261</v>
@@ -5872,10 +6937,10 @@
         <v>262</v>
       </c>
       <c r="D59" t="s">
-        <v>262</v>
+        <v>332</v>
       </c>
       <c r="E59" t="s">
-        <v>348</v>
+        <v>382</v>
       </c>
     </row>
     <row r="60" spans="1:5">
@@ -5889,10 +6954,10 @@
         <v>263</v>
       </c>
       <c r="D60" t="s">
-        <v>317</v>
+        <v>333</v>
       </c>
       <c r="E60" t="s">
-        <v>317</v>
+        <v>333</v>
       </c>
     </row>
     <row r="61" spans="1:5">
@@ -5906,10 +6971,10 @@
         <v>264</v>
       </c>
       <c r="D61" t="s">
-        <v>318</v>
+        <v>334</v>
       </c>
       <c r="E61" t="s">
-        <v>264</v>
+        <v>383</v>
       </c>
     </row>
     <row r="62" spans="1:5">
@@ -5926,7 +6991,7 @@
         <v>265</v>
       </c>
       <c r="E62" t="s">
-        <v>265</v>
+        <v>384</v>
       </c>
     </row>
     <row r="63" spans="1:5">
@@ -5940,10 +7005,10 @@
         <v>266</v>
       </c>
       <c r="D63" t="s">
-        <v>319</v>
+        <v>335</v>
       </c>
       <c r="E63" t="s">
-        <v>319</v>
+        <v>335</v>
       </c>
     </row>
     <row r="64" spans="1:5">
@@ -5977,7 +7042,7 @@
         <v>268</v>
       </c>
       <c r="E65" t="s">
-        <v>349</v>
+        <v>385</v>
       </c>
     </row>
     <row r="66" spans="1:5">
@@ -5991,10 +7056,10 @@
         <v>269</v>
       </c>
       <c r="D66" t="s">
-        <v>320</v>
+        <v>269</v>
       </c>
       <c r="E66" t="s">
-        <v>320</v>
+        <v>269</v>
       </c>
     </row>
     <row r="67" spans="1:5">
@@ -6008,10 +7073,10 @@
         <v>270</v>
       </c>
       <c r="D67" t="s">
-        <v>321</v>
+        <v>336</v>
       </c>
       <c r="E67" t="s">
-        <v>321</v>
+        <v>336</v>
       </c>
     </row>
     <row r="68" spans="1:5">
@@ -6028,7 +7093,7 @@
         <v>271</v>
       </c>
       <c r="E68" t="s">
-        <v>271</v>
+        <v>386</v>
       </c>
     </row>
     <row r="69" spans="1:5">
@@ -6042,10 +7107,10 @@
         <v>272</v>
       </c>
       <c r="D69" t="s">
+        <v>337</v>
+      </c>
+      <c r="E69" t="s">
         <v>272</v>
-      </c>
-      <c r="E69" t="s">
-        <v>350</v>
       </c>
     </row>
     <row r="70" spans="1:5">
@@ -6059,10 +7124,10 @@
         <v>273</v>
       </c>
       <c r="D70" t="s">
-        <v>322</v>
+        <v>338</v>
       </c>
       <c r="E70" t="s">
-        <v>273</v>
+        <v>387</v>
       </c>
     </row>
     <row r="71" spans="1:5">
@@ -6076,10 +7141,10 @@
         <v>274</v>
       </c>
       <c r="D71" t="s">
-        <v>323</v>
+        <v>339</v>
       </c>
       <c r="E71" t="s">
-        <v>274</v>
+        <v>388</v>
       </c>
     </row>
     <row r="72" spans="1:5">
@@ -6093,7 +7158,7 @@
         <v>275</v>
       </c>
       <c r="D72" t="s">
-        <v>324</v>
+        <v>340</v>
       </c>
       <c r="E72" t="s">
         <v>275</v>
@@ -6110,7 +7175,7 @@
         <v>276</v>
       </c>
       <c r="D73" t="s">
-        <v>325</v>
+        <v>276</v>
       </c>
       <c r="E73" t="s">
         <v>276</v>
@@ -6127,10 +7192,10 @@
         <v>277</v>
       </c>
       <c r="D74" t="s">
-        <v>326</v>
+        <v>341</v>
       </c>
       <c r="E74" t="s">
-        <v>326</v>
+        <v>341</v>
       </c>
     </row>
     <row r="75" spans="1:5">
@@ -6144,7 +7209,7 @@
         <v>278</v>
       </c>
       <c r="D75" t="s">
-        <v>278</v>
+        <v>342</v>
       </c>
       <c r="E75" t="s">
         <v>278</v>
@@ -6161,10 +7226,10 @@
         <v>279</v>
       </c>
       <c r="D76" t="s">
-        <v>279</v>
+        <v>343</v>
       </c>
       <c r="E76" t="s">
-        <v>351</v>
+        <v>343</v>
       </c>
     </row>
     <row r="77" spans="1:5">
@@ -6178,10 +7243,10 @@
         <v>280</v>
       </c>
       <c r="D77" t="s">
-        <v>327</v>
+        <v>344</v>
       </c>
       <c r="E77" t="s">
-        <v>327</v>
+        <v>344</v>
       </c>
     </row>
     <row r="78" spans="1:5">
@@ -6195,10 +7260,10 @@
         <v>281</v>
       </c>
       <c r="D78" t="s">
-        <v>281</v>
+        <v>345</v>
       </c>
       <c r="E78" t="s">
-        <v>281</v>
+        <v>345</v>
       </c>
     </row>
     <row r="79" spans="1:5">
@@ -6229,10 +7294,10 @@
         <v>283</v>
       </c>
       <c r="D80" t="s">
-        <v>283</v>
+        <v>346</v>
       </c>
       <c r="E80" t="s">
-        <v>283</v>
+        <v>389</v>
       </c>
     </row>
     <row r="81" spans="1:5">
@@ -6246,10 +7311,10 @@
         <v>284</v>
       </c>
       <c r="D81" t="s">
-        <v>284</v>
+        <v>347</v>
       </c>
       <c r="E81" t="s">
-        <v>284</v>
+        <v>390</v>
       </c>
     </row>
     <row r="82" spans="1:5">
@@ -6266,7 +7331,7 @@
         <v>285</v>
       </c>
       <c r="E82" t="s">
-        <v>285</v>
+        <v>391</v>
       </c>
     </row>
     <row r="83" spans="1:5">
@@ -6280,10 +7345,10 @@
         <v>286</v>
       </c>
       <c r="D83" t="s">
-        <v>328</v>
+        <v>348</v>
       </c>
       <c r="E83" t="s">
-        <v>352</v>
+        <v>286</v>
       </c>
     </row>
     <row r="84" spans="1:5">
@@ -6297,10 +7362,10 @@
         <v>287</v>
       </c>
       <c r="D84" t="s">
-        <v>329</v>
+        <v>349</v>
       </c>
       <c r="E84" t="s">
-        <v>329</v>
+        <v>349</v>
       </c>
     </row>
     <row r="85" spans="1:5">
@@ -6314,10 +7379,10 @@
         <v>288</v>
       </c>
       <c r="D85" t="s">
-        <v>330</v>
+        <v>288</v>
       </c>
       <c r="E85" t="s">
-        <v>330</v>
+        <v>288</v>
       </c>
     </row>
     <row r="86" spans="1:5">
@@ -6331,10 +7396,10 @@
         <v>289</v>
       </c>
       <c r="D86" t="s">
-        <v>289</v>
+        <v>350</v>
       </c>
       <c r="E86" t="s">
-        <v>289</v>
+        <v>350</v>
       </c>
     </row>
     <row r="87" spans="1:5">
@@ -6348,10 +7413,10 @@
         <v>290</v>
       </c>
       <c r="D87" t="s">
-        <v>290</v>
+        <v>351</v>
       </c>
       <c r="E87" t="s">
-        <v>290</v>
+        <v>392</v>
       </c>
     </row>
     <row r="88" spans="1:5">
@@ -6382,10 +7447,10 @@
         <v>292</v>
       </c>
       <c r="D89" t="s">
-        <v>331</v>
+        <v>352</v>
       </c>
       <c r="E89" t="s">
-        <v>331</v>
+        <v>292</v>
       </c>
     </row>
     <row r="90" spans="1:5">
@@ -6399,10 +7464,10 @@
         <v>293</v>
       </c>
       <c r="D90" t="s">
-        <v>293</v>
+        <v>353</v>
       </c>
       <c r="E90" t="s">
-        <v>293</v>
+        <v>353</v>
       </c>
     </row>
     <row r="91" spans="1:5">
@@ -6416,10 +7481,10 @@
         <v>294</v>
       </c>
       <c r="D91" t="s">
+        <v>354</v>
+      </c>
+      <c r="E91" t="s">
         <v>294</v>
-      </c>
-      <c r="E91" t="s">
-        <v>353</v>
       </c>
     </row>
     <row r="92" spans="1:5">
@@ -6436,7 +7501,7 @@
         <v>295</v>
       </c>
       <c r="E92" t="s">
-        <v>354</v>
+        <v>295</v>
       </c>
     </row>
     <row r="93" spans="1:5">
@@ -6453,7 +7518,7 @@
         <v>296</v>
       </c>
       <c r="E93" t="s">
-        <v>355</v>
+        <v>393</v>
       </c>
     </row>
     <row r="94" spans="1:5">
@@ -6467,10 +7532,10 @@
         <v>297</v>
       </c>
       <c r="D94" t="s">
-        <v>332</v>
+        <v>355</v>
       </c>
       <c r="E94" t="s">
-        <v>332</v>
+        <v>297</v>
       </c>
     </row>
     <row r="95" spans="1:5">
@@ -6484,10 +7549,10 @@
         <v>298</v>
       </c>
       <c r="D95" t="s">
-        <v>298</v>
+        <v>356</v>
       </c>
       <c r="E95" t="s">
-        <v>298</v>
+        <v>394</v>
       </c>
     </row>
     <row r="96" spans="1:5">
@@ -6501,10 +7566,10 @@
         <v>299</v>
       </c>
       <c r="D96" t="s">
-        <v>299</v>
+        <v>357</v>
       </c>
       <c r="E96" t="s">
-        <v>356</v>
+        <v>395</v>
       </c>
     </row>
     <row r="97" spans="1:5">
@@ -6518,10 +7583,10 @@
         <v>300</v>
       </c>
       <c r="D97" t="s">
-        <v>300</v>
+        <v>358</v>
       </c>
       <c r="E97" t="s">
-        <v>300</v>
+        <v>396</v>
       </c>
     </row>
     <row r="98" spans="1:5">
@@ -6535,7 +7600,7 @@
         <v>301</v>
       </c>
       <c r="D98" t="s">
-        <v>333</v>
+        <v>359</v>
       </c>
       <c r="E98" t="s">
         <v>301</v>
@@ -6552,10 +7617,10 @@
         <v>302</v>
       </c>
       <c r="D99" t="s">
-        <v>334</v>
+        <v>360</v>
       </c>
       <c r="E99" t="s">
-        <v>334</v>
+        <v>360</v>
       </c>
     </row>
     <row r="100" spans="1:5">
@@ -6569,10 +7634,10 @@
         <v>303</v>
       </c>
       <c r="D100" t="s">
-        <v>303</v>
+        <v>361</v>
       </c>
       <c r="E100" t="s">
-        <v>303</v>
+        <v>397</v>
       </c>
     </row>
     <row r="101" spans="1:5">
